--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487189_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487189_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. KEITH CAMARA</t>
+          <t>A. LOPEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.4664</v>
+        <v>1.6878</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2471</v>
+        <v>1.2183</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2193</v>
+        <v>0.4695</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.4332</v>
+        <v>1.6842</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.0833</v>
+        <v>1.0816</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3499</v>
+        <v>0.6026</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.1783</v>
+        <v>2.1513</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.0466</v>
+        <v>2.0699</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.1317</v>
+        <v>0.0814</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.2549</v>
+        <v>-0.4671</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.0367</v>
+        <v>-0.9883</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7818000000000001</v>
+        <v>0.5212</v>
       </c>
       <c r="P2" t="n">
-        <v>2.7021</v>
+        <v>-0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R2" t="n">
-        <v>2.7021</v>
+        <v>0.965</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0727</v>
+        <v>0.0036</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1396</v>
+        <v>0.0321</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.2123</v>
+        <v>-0.0284</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2702</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.9843</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. LOPEZ FERNANDEZ</t>
+          <t>D. KEITH CAMARA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0602</v>
+        <v>0.9449</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8584000000000001</v>
+        <v>-0.435</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2018</v>
+        <v>1.3799</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6842</v>
+        <v>-2.4332</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0816</v>
+        <v>-2.0833</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6026</v>
+        <v>-0.3499</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1513</v>
+        <v>-1.1783</v>
       </c>
       <c r="K3" t="n">
-        <v>2.0699</v>
+        <v>-0.0466</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0814</v>
+        <v>-1.1317</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4671</v>
+        <v>-1.2549</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9883</v>
+        <v>-2.0367</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5212</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>2.7021</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.965</v>
+        <v>2.7021</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.624</v>
+        <v>-0.5942</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3278</v>
+        <v>0.4574</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2961</v>
+        <v>-1.0517</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.2702</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.9843</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. NDOYE</t>
+          <t>J. OTERO GONZALEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.868</v>
+        <v>0.7144</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2117</v>
+        <v>0.3745</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3437</v>
+        <v>0.3399</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5057</v>
+        <v>0.4035</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.08690000000000001</v>
+        <v>-0.7982</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5926</v>
+        <v>1.2017</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7675</v>
+        <v>3.3331</v>
       </c>
       <c r="K4" t="n">
-        <v>1.035</v>
+        <v>2.0799</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7326</v>
+        <v>1.2531</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2618</v>
+        <v>-2.9295</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1219</v>
+        <v>-2.8781</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.14</v>
+        <v>-0.0514</v>
       </c>
       <c r="P4" t="n">
-        <v>0.193</v>
+        <v>0.579</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.8951</v>
       </c>
       <c r="R4" t="n">
-        <v>0.193</v>
+        <v>3.4741</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7833</v>
+        <v>-0.6385</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4442</v>
+        <v>-0.0634</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3391</v>
+        <v>-0.5750999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.614</v>
+        <v>0.3704</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.614</v>
+        <v>0.3704</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. REYES ABAD</t>
+          <t>N. NDOYE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6256</v>
+        <v>0.5409</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1562</v>
+        <v>1.9113</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5306</v>
+        <v>-1.3705</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.8046</v>
+        <v>0.5057</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.3847</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4199</v>
+        <v>0.5926</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.082</v>
+        <v>1.7675</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5534</v>
+        <v>1.035</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6355</v>
+        <v>0.7326</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.7225</v>
+        <v>-1.2618</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.9381</v>
+        <v>-1.1219</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2156</v>
+        <v>-0.14</v>
       </c>
       <c r="P5" t="n">
-        <v>3.4741</v>
+        <v>0.193</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.4741</v>
+        <v>0.193</v>
       </c>
       <c r="S5" t="n">
-        <v>1.8402</v>
+        <v>0.4561</v>
       </c>
       <c r="T5" t="n">
-        <v>1.8945</v>
+        <v>0.1438</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0543</v>
+        <v>0.3123</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.8842</v>
+        <v>-0.614</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6562</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.228</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. OTERO GONZALEZ</t>
+          <t>F. AMBROSONI ÁLVAREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3495</v>
+        <v>0.4187</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2045</v>
+        <v>1.4085</v>
       </c>
       <c r="F6" t="n">
-        <v>0.554</v>
+        <v>-0.9898</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4035</v>
+        <v>-2.154</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7982</v>
+        <v>-0.7702</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2017</v>
+        <v>-1.3838</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3331</v>
+        <v>1.1697</v>
       </c>
       <c r="K6" t="n">
-        <v>2.0799</v>
+        <v>2.375</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2531</v>
+        <v>-1.2052</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.9295</v>
+        <v>-3.3237</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.8781</v>
+        <v>-3.1451</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0514</v>
+        <v>-0.1785</v>
       </c>
       <c r="P6" t="n">
-        <v>0.579</v>
+        <v>1.3511</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.8951</v>
+        <v>-1.9301</v>
       </c>
       <c r="R6" t="n">
-        <v>3.4741</v>
+        <v>3.2811</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0034</v>
+        <v>-1.1921</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6424</v>
+        <v>-0.2449</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.361</v>
+        <v>-0.9472</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3704</v>
+        <v>2.4137</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.4137</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3704</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0427</v>
+        <v>0.3707</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8616</v>
+        <v>-0.5016</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8188</v>
+        <v>0.8724</v>
       </c>
       <c r="G7" t="n">
         <v>0.2513</v>
@@ -1000,13 +1000,13 @@
         <v>0.579</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2168</v>
+        <v>0.1966</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2829</v>
+        <v>0.077</v>
       </c>
       <c r="U7" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.1196</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6562</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2871</v>
+        <v>-0.4804</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1494</v>
+        <v>-0.151</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4365</v>
+        <v>-0.3294</v>
       </c>
       <c r="G8" t="n">
         <v>-0.7141</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.427</v>
+        <v>0.2337</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4297</v>
+        <v>0.1292</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0026</v>
+        <v>0.1044</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. AMBROSONI ÁLVAREZ</t>
+          <t>A. REYES ABAD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7621</v>
+        <v>-1.2335</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3882</v>
+        <v>-0.1674</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1504</v>
+        <v>-1.066</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.154</v>
+        <v>-2.8046</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7702</v>
+        <v>-2.3847</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3838</v>
+        <v>-0.4199</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1697</v>
+        <v>-0.082</v>
       </c>
       <c r="K9" t="n">
-        <v>2.375</v>
+        <v>0.5534</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2052</v>
+        <v>-0.6355</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.3237</v>
+        <v>-2.7225</v>
       </c>
       <c r="N9" t="n">
-        <v>-3.1451</v>
+        <v>-2.9381</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1785</v>
+        <v>0.2156</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3511</v>
+        <v>3.4741</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.2811</v>
+        <v>3.4741</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.3729</v>
+        <v>-0.0188</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2651</v>
+        <v>0.5708</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.1078</v>
+        <v>-0.5897</v>
       </c>
       <c r="V9" t="n">
-        <v>2.4137</v>
+        <v>-1.8842</v>
       </c>
       <c r="W9" t="n">
-        <v>2.4137</v>
+        <v>-0.6562</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1597</v>
+        <v>-1.2594</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9586</v>
+        <v>1.7786</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.1183</v>
+        <v>-3.038</v>
       </c>
       <c r="G10" t="n">
         <v>1.0127</v>
@@ -1234,13 +1234,13 @@
         <v>3.0881</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.1145</v>
+        <v>-1.2142</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1461</v>
+        <v>-0.3262</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9684</v>
+        <v>-0.8881</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2859</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9946</v>
+        <v>-3.6883</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9101</v>
+        <v>-2.5502</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0845</v>
+        <v>-1.1381</v>
       </c>
       <c r="G11" t="n">
         <v>-2.0924</v>
@@ -1312,13 +1312,13 @@
         <v>0.579</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2882</v>
+        <v>0.0182</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6398</v>
+        <v>-0.2799</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3516</v>
+        <v>0.2981</v>
       </c>
       <c r="V11" t="n">
         <v>-1.228</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8765</v>
+        <v>-1.9842</v>
       </c>
       <c r="E12" t="n">
-        <v>1.993399999999999</v>
+        <v>2.886</v>
       </c>
       <c r="F12" t="n">
         <v>-4.8701</v>
@@ -1360,7 +1360,7 @@
         <v>-6.9762</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6353000000000003</v>
+        <v>0.6353000000000005</v>
       </c>
       <c r="J12" t="n">
         <v>9.776400000000001</v>
@@ -1369,7 +1369,7 @@
         <v>10.219</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.4424999999999998</v>
+        <v>-0.4425000000000002</v>
       </c>
       <c r="M12" t="n">
         <v>-16.117</v>
@@ -1390,13 +1390,13 @@
         <v>18.3355</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.642</v>
+        <v>-2.7496</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3960999999999998</v>
+        <v>0.4958999999999998</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.2457</v>
+        <v>-3.2458</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6140000000000003</v>
@@ -1405,7 +1405,7 @@
         <v>3.2292</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.843100000000001</v>
+        <v>-3.8431</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.933</v>
+        <v>8.9842</v>
       </c>
       <c r="E13" t="n">
-        <v>7.0229</v>
+        <v>6.0215</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9102</v>
+        <v>2.9627</v>
       </c>
       <c r="G13" t="n">
         <v>6.0924</v>
@@ -1468,13 +1468,13 @@
         <v>1.5441</v>
       </c>
       <c r="S13" t="n">
-        <v>2.6049</v>
+        <v>1.6561</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6142</v>
+        <v>0.6128</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9908</v>
+        <v>1.0433</v>
       </c>
       <c r="V13" t="n">
         <v>1.6217</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.019</v>
+        <v>5.5186</v>
       </c>
       <c r="E14" t="n">
-        <v>5.7363</v>
+        <v>4.835</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2827</v>
+        <v>0.6836</v>
       </c>
       <c r="G14" t="n">
         <v>5.3301</v>
@@ -1546,13 +1546,13 @@
         <v>1.158</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3953</v>
+        <v>0.895</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6155</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2201</v>
+        <v>0.1807</v>
       </c>
       <c r="V14" t="n">
         <v>0.06560000000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.0358</v>
+        <v>5.2358</v>
       </c>
       <c r="E15" t="n">
-        <v>3.626</v>
+        <v>3.8263</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4098</v>
+        <v>1.4095</v>
       </c>
       <c r="G15" t="n">
         <v>2.2046</v>
@@ -1624,13 +1624,13 @@
         <v>1.3511</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2095</v>
+        <v>0.4095</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1361</v>
+        <v>0.0641</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3456</v>
+        <v>0.3453</v>
       </c>
       <c r="V15" t="n">
         <v>2.2357</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9652</v>
+        <v>3.5615</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5008</v>
+        <v>2.402</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4644</v>
+        <v>1.1594</v>
       </c>
       <c r="G16" t="n">
         <v>2.3577</v>
@@ -1702,13 +1702,13 @@
         <v>1.3511</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0649</v>
+        <v>0.5314</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6993</v>
+        <v>0.202</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3656</v>
+        <v>0.3295</v>
       </c>
       <c r="V16" t="n">
         <v>1.2513</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1108</v>
+        <v>0.964</v>
       </c>
       <c r="E17" t="n">
-        <v>1.236</v>
+        <v>1.0357</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1252</v>
+        <v>-0.0717</v>
       </c>
       <c r="G17" t="n">
         <v>0.6005</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5103</v>
+        <v>0.3635</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5486</v>
+        <v>0.3483</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0383</v>
+        <v>0.0152</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1863</v>
+        <v>-0.1391</v>
       </c>
       <c r="E18" t="n">
-        <v>0.07969999999999999</v>
+        <v>-0.2208</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.266</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="G18" t="n">
         <v>-0.6252</v>
@@ -1858,13 +1858,13 @@
         <v>0.579</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1401</v>
+        <v>-0.0929</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2512</v>
+        <v>-0.0492</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3913</v>
+        <v>-0.0436</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5066</v>
+        <v>-2.6868</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1325</v>
+        <v>-1.6332</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3742</v>
+        <v>-1.0536</v>
       </c>
       <c r="G19" t="n">
         <v>-3.6219</v>
@@ -1936,13 +1936,13 @@
         <v>0.579</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1924</v>
+        <v>1.0123</v>
       </c>
       <c r="T19" t="n">
-        <v>1.4238</v>
+        <v>0.9231</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2313</v>
+        <v>0.0892</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6562</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.4838</v>
+        <v>-3.7104</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.7684</v>
+        <v>-1.9672</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7154</v>
+        <v>-1.7432</v>
       </c>
       <c r="G20" t="n">
         <v>-2.3797</v>
@@ -2014,13 +2014,13 @@
         <v>1.158</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0159</v>
+        <v>0.7575</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5063</v>
+        <v>0.2948</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4904</v>
+        <v>0.4627</v>
       </c>
       <c r="V20" t="n">
         <v>0.614</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.6629</v>
+        <v>-4.3222</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.6015</v>
+        <v>-4.5014</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0613</v>
+        <v>0.1793</v>
       </c>
       <c r="G21" t="n">
         <v>0.1797</v>
@@ -2092,13 +2092,13 @@
         <v>1.3511</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0568</v>
+        <v>0.3976</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0423</v>
+        <v>0.1425</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0145</v>
+        <v>0.2551</v>
       </c>
       <c r="V21" t="n">
         <v>-2.3903</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-9.347799999999999</v>
+        <v>-7.8589</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.8291</v>
+        <v>-4.9279</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.5186</v>
+        <v>-2.931</v>
       </c>
       <c r="G22" t="n">
         <v>-3.7973</v>
@@ -2170,13 +2170,13 @@
         <v>1.5441</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1065</v>
+        <v>0.3824</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9082</v>
+        <v>-0.0069</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1983</v>
+        <v>0.3893</v>
       </c>
       <c r="V22" t="n">
         <v>-2.1278</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>2.8764</v>
+        <v>5.546700000000003</v>
       </c>
       <c r="E23" t="n">
-        <v>4.870199999999999</v>
+        <v>4.870000000000002</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9936</v>
+        <v>0.6766999999999999</v>
       </c>
       <c r="G23" t="n">
         <v>6.340900000000001</v>
@@ -2248,13 +2248,13 @@
         <v>10.6155</v>
       </c>
       <c r="S23" t="n">
-        <v>3.6418</v>
+        <v>6.312399999999999</v>
       </c>
       <c r="T23" t="n">
         <v>3.2457</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3964000000000001</v>
+        <v>3.0667</v>
       </c>
       <c r="V23" t="n">
         <v>0.6140000000000003</v>
